--- a/秋招投递追踪表.xlsx
+++ b/秋招投递追踪表.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3941,6 +3941,1784 @@
       <c r="Q44" t="inlineStr">
         <is>
           <t>类型:秋招提前批; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>169</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>国泰海通证券</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>互联网业务管培生</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>上海、深圳、北京</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://www.jrzp.com/xiaozhaoView/5607953.shtml</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>国泰君安+海通合并，互联网券商方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>170</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>中信证券</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>校招培训生（分支机构）</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>金融策略</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>北京、上海、深圳、杭州、广州等全国</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://careers.citics.com</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026年暑期实习转正通道，面向2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>171</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>中信证券</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>校招培训生（杭州）</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://m.liepin.com/job/1983340477.shtml</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>172</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>华泰证券</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>财富管理与机构业务岗（2027届暑期实习）</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>金融策略</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>全国30个省市</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://wecruit.hotjob.cn/SU6419745cbef57c635fe10142/pb/index.html</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2027届暑期实习，优秀者优先参与秋招</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>173</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>红塔证券</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>战略评估岗、投资研究岗</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>昆明、上海</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/JeO8vUk1md2ECzMoDGB3-w</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>战略评估岗适合金融专业</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>174</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>腾讯</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026实习生招聘（产品/运营/市场/职能）</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>北京、上海、深圳、广州</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2027届（2026.9-2027.12毕业）</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://join.qq.com/</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>实习生招聘，优秀者可留用转正</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>175</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>阿里巴巴</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2027届全球实习生招聘（产品/运营/商务拓展）</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>杭州、北京、上海</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2027届（2026.11-2027.10毕业）</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://talent.alibaba.com/</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>AI岗位占比超80%，但产品/运营/商务拓展岗也有开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>176</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>字节跳动</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ByteIntern2026实习生（产品/运营/市场/数据分析）</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>北京、上海、深圳、杭州</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2027届（2026.9-2027.8毕业）</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://jobs.bytedance.com/campus</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>整体转正率约55%，覆盖抖音/TikTok等业务</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>177</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>美团</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2027届转正实习（商业分析/战略/运营/产品）</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>商业分析/经营分析</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>北京、上海、深圳</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://zhaopin.meituan.com/</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>3000+转正实习岗位，含大模型人才校招专项</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>178</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2027届秋招提前批（运营/供应链/产品/市场）</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>策略运营</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://campus.jd.com/</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2.5万岗位，含1万实习生岗</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>179</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>科大讯飞</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2027届常规校招（产品/职能/市场类）</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>合肥、北京、上海</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://campus.iflytek.com/</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>技术类60%，产品/职能类也有开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>180</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2027届实习生招聘（财经/销售/市场/供应链）</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>财务/审计</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>深圳、北京、上海</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://career.huawei.com/</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>财经方向：资金/财务/税务/风控等岗位</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>181</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>贝恩咨询 (Bain)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2027届全职助理顾问 (Associate Consultant)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>北京、上海</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://www.bain.com/careers/</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>MBB之一，中国大陆地区9月2日截止</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>182</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>麦肯锡 (McKinsey)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2027 Summer Business Analyst</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>北京、上海</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://www.mckinsey.com/careers/students</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>MBB之一，即将截止(28天后)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>183</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>招商银行</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2027秋招提前批（管培/金融科技/运营/营销）</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>风险管理/合规</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>北京、上海、深圳、广州、杭州等全国</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://career.cmbchina.com/</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>提前批7-8月启动，可报5个岗位</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>184</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>华夏银行</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2027秋招提前批（管培/运营/营销）</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>策略运营</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>北京、上海等全国</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://www.hxb.com.cn/</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>提前批7-8月</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>185</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>国泰海通资管</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>基金/资管</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>固收投研/权益投研/风险管理/品牌宣传</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>投资/行研</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>上海、北京、深圳</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2027届（2026.8-2027.7毕业）</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://www.htsc-am.com/</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>管理规模超7400亿，走完校招流程中</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>186</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2027届实习生招聘（市场/销售/供应链/职能）</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>深圳、北京、上海等全国</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://job.byd.com/</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>实习考核通过可直签正式offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>187</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>大疆 (DJI)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2027届秋招正式批（市场/运营/供应链/职能）</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>深圳、北京、上海</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://we.dji.com/</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>7月30日全品类正式批启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>188</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>通怡投资</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PE/VC</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>产业研究员/产品助理</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>投资/行研</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/5qCW-mJoY6ZjBF3asO_yXQ</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>私募投资公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>189</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>复星集团</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PE/VC</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>集团下属各公司岗位（投资/战略/财务/运营）</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/oiNKs0cLUht87q-TzLuNWA</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>多元化投资集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>190</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>五矿国际信托</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>信托</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>战略发展研究院战略研究岗/合规风控/风险管理岗</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/8NHvi8jBjL9x8E3zvl_Eug</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>信托公司，战略/风控岗位适合金融专业</t>
         </is>
       </c>
     </row>
@@ -3955,7 +5733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4053,6 +5831,31 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>65</v>
+      </c>
+      <c r="E4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>互联网/科技(7), 券商(5), 咨询(2) + WebSearch</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/秋招投递追踪表.xlsx
+++ b/秋招投递追踪表.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q221"/>
+  <dimension ref="A1:Q265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -17683,6 +17683,3394 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>598</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>紫光同创</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>软件开发工程师 软件测试工程师 混合信号设计工程师 数字电路设计工程师FPGa开发工程师嵌入式应用开发工程师销售工程师 测试开发工程师 FPGA测试设计工程师C</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>深圳成都北京上海</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>https://young.yingjiesheng.com/xyzlogin?ctmid=d07b2450-a61b-4cfe-a05a-b5ea2d00a8f3&amp;amp</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>599</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>宇通集团</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>能源</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>财经管培生人力管培生研发管培生生产管理管培生供应链管培生国内营销管培生(销售方向)国内营销管培生(售后方向)海外营销管培生(销售方向)海外营销管培生(售后方向)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>https://wecruit.hotjob.cn/SU649796b60dcad412ce9c4bbd/pb/school.html</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>600</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>科大讯飞</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>AI 研究算法工程师（多方向）语音大模型方向、认知大模型方向、多模态大模型方向、智能语音方向、自然语言处理方向、计算机视觉方向、深度学习框架和平台方向、大模型训</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>北京, 上海, 合肥, 广州, 西安</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>https://iflytek.zhiye.com/4/jobs</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>601</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>航空工业通飞</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>国企</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>财务岗，研发设计岗，研发技术工程师，智能制造工程师，无损检测工程师，应急研究岗，职能类岗，营销类岗，维修工程师，运行管理岗兼签派工程师，运行标准岗，工艺技术岗，</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>石家庄, 苏州, 太仓, 景德镇, 武汉, 荆门, 珠海, 贵阳, 安顺, 西安, 汉中</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>https://www.kdocs.cn/l/cqOCE7kUZgUZ</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>602</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>中创新航</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>国企</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>设备工程师, 电芯工艺工程师, 集成工艺工程师, 电芯质量工程师, 集成质量工程师, 现场IE工程师岗, 其他技术类, 安全工程师, 主计划, 生产计划岗, （</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>江门</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/kjzMMCOo9aCYenu07M1uAg</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>603</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>利得基金</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>应届生岗位:机械销售助理、利得研究院-研究助理、营销支持助理, 实习生岗位:利得研究院-研究实习生、机构销售实习生、互联网产品实习生、开发实习生(AI方向)数据</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>上海北京深圳</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/g0cVuqbETbWU48BZg6RcrQ</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>604</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>天龙世纪</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>其他,科技</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Android Framework开发工程师, 高级Android驱动工程师, 高级Layout工程师, 硬件测试工程师, 整机测试工程师, 高级基带工程师, </t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>郑州, 深圳</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/__cWrPwWT03iFt925jZ3hQ</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>605</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>中航通用飞机有限责任公司</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>国企</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>财务岗、研发设计岗、研发技术工程师、智能制造工程师、无损检测工程师、应急研究岗、职能类岗、营销类岗、维修工程师、运行管理岗兼签派工程师、运行标准岗、工艺技术岗、</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>石家庄, 苏州, 景德镇, 武汉, 荆门, 珠海, 贵阳, 安顺, 西安, 汉中</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>https://www.kdocs.cn/l/cqOCE7kUZgUZ</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>606</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>锐石创芯</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>RF设计工程师(PA)RF设计工程师(SwitchaLNA) Analog IC设计工程师滤波器设计工程师 工艺工程师 生产计划工程师 采购工程师 AE射频器件</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>财务/审计</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>重庆深圳上海成都</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>https://radrocktech.jobs.feishu.cn/531403/position/list?spread=Q13728Z</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>607</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>长飞光纤光缆股份有限公司</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>AI大模型工程师, 产品研发工程师, 光学研发工程师, 硬件研发工程师, 软件研发工程师, 技术情报工程师, 工艺工程师, 机械工程师, 暖通工程师, 技术支持</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>武汉, 潜江</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>https://yofc2.zhiye.com/campus/jobs</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>608</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>天锐星通</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>模拟IC设计工程师, 射频IC设计工程师, 天线工程师, 射频工程师, 硬件工程师, 结构工程师, 逻辑工程师, 嵌入式工程师, 测试方法研究工程师, AI a</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>上海, 南京, 成都</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>https://t-ray.zhiye.com/campus/jobs</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>609</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>BrainCo强脑科技</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>机器人产品专家、产品工程师、工业设计师、应用工程师、用户体验工程师、AI赋能设计师、整机硬件架构师、电子硬件工程师、机械结构工程师、测试工程师、电机工程师、工艺</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>https://wj.qq.com/s2/26996638/8308/</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>610</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>新东方大学生学习与发展中心</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">计算机408教研实习生, 西医306教研实习生, 产品运营实习生, 考研学习顾问, 考研学习管理师, 四六级学习管理师, 考研线上运营专员, 专升本学习顾问, </t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>策略运营</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>https://zhaopin.xdf.cn/jobs?activityGuid=3a4fd7d6-2003-4139-b9a9-4a39f337af97</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>611</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>易动宇航</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>高端装备与国防科技/航空航天</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>系统工程师 产品工程师 硬件工程师 电源工程师 电气工程师结构设计师 机电设计师 元器件工程师工艺工程师 研发助理测试工程师 装配工程师质量工程师财务人员人力资</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>北京上海</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/zzQllc6-Mtp_7QwQBsPagg</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>612</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>芯动科技</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>科技,其他</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>数字IC设计工程师, 数字IC验证工程师, 模拟IC设计工程师, DSP算法及建模工程师, 高性能计算工程师, GPU软件工程师, AI软件栈工程师, 嵌入式软</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>大连, 上海, 苏州, 武汉, 珠海, 成都, 西安</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>https://innosilicon.zhiye.com/</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>613</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>捷迅光电</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>海外销售经理, 售后服务工程师, 国内销售经理, 品牌专员, 软件工程师, 机械工程师, 电气工程师, 应用工程师, 采购工程师, 工艺工程师, 仓管员, 质量</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>风险管理</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/EVrCWbbyAfAbJ9ZV5xPPkg</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>614</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>智元机器人</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>研究类, 算法类, 软件类, 硬件类, 结构类, 质量类, 关节类, 测试类, 系统架构类, 安全工程类, 解决方案类, 项目管理类, 标准与知识产权类, 工业</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>北京, 上海, 深圳, 香港, 澳门, 海外</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>https://agirobot.jobs.feishu.cn/campusrecruitment</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>615</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>航天五院卫星应用总体部</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>国企</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>体系总体, 算法工程, 系统设计与实施, 软件开发、通信与信息系统、电子信息工程、通信工程、物联网应用技术、军事通信学、数据科学与大数据技术、软件工程、软件与信</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/w4r5Nv160e-gLg2buL3iLA</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>616</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>麦米电气</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>其他,科技</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>新型电力电子拓扑与控制, 储能变流器并网技术, 电力电子数字化仿真, AIDC数据中心供电技术, 电力电子磁件设计, 激光与电弧物理研究, 涡旋压缩机, 流体仿</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>南京, 杭州, 武汉, 长沙, 深圳, 西安</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>https://wecruit.hotjob.cn/SU6282075e0dcad413c09efe26/pb/school.html?projectCode=201301&amp;showProjectBanner=true</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>617</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>中国电科网络通信研究院</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>通信总体设计工程师, 基带工程师, 射频开发工程师, 天线系统设计工程师, 信号处理算法工程师, 大数据与人工智能工程师, 算法开发工程师, 软件总体设计工程师</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>https://campus.51job.com/2026cetc54/about1.html</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>618</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>正浩EcoFlow</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>新能源,科技</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>电力电子硬件工程师, 电力电子软件工程师, AI算法工程师, 嵌入式软件工程师, 后端工程师, 结构工程师, 软件产品经理</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>苏州, 深圳, 西安</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>https://jobs.ecoflow.com/602892/position/list?keywords=&amp;category=&amp;location=&amp;project=7660773517268699430&amp;type=&amp;job_hot_flag=&amp;current=1&amp;limit=10&amp;functionCategory=&amp;tag=</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>619</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>卓驭</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>端到端领航算法工程师, 端到端模型算法工程师, 大模型训练优化算法工程师, 大模型推理优化算法工程师, 多模态大模型预训练算法工程师, 多模态大模型后训练算法工</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>北京, 上海, 深圳, 香港</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>https://we.zyt.com/campus/jobs</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>620</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>信步科技</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>硬件 软件产品 市场供应链职能</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>https://seavo.hotjob.cn/</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>621</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>爱凡哲投资</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>量化策略研究员量化开发工程师股票高频算法量化AI工程师 市场专员产品运营投资经理助理/交易员</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>上海 成都</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/PaCfz4jPi067slfL-SuyyQ</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>622</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>第一创业证券</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>2026暑期实习（可转正）</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>北京/上海/广州/深圳</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>https://www.firstcapital.com.cn/</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 面向2026.9-2027.8毕业</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>623</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>2027届暑期实习-行业研究/风险管理/指数研究/管培/资管产品等</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>https://www.eastmoney.com/</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 有转正机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>624</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>中国银行</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>2027秋招-多岗位</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>全国/北京/上海</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>https://www.boc.cn/</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 网申2026年9月5日-10月10日</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>625</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>贝恩咨询</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>2027届全职咨询顾问</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>上海/北京</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>https://www.bain.com/careers/</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 非北美地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>626</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>美团</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>战略与投资平台-2027届暑期转正实习</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>北京/上海/深圳</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>https://campus.meituan.com/</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 战略投资方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>627</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>腾讯</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>青云计划-2027校园招聘</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>深圳/北京/上海/广州</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>https://join.qq.com/</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 7月15日启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>628</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>2027届实习生招聘-财经类/法务类</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>财务/审计</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>深圳/上海/北京/东莞</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>https://career.huawei.com/</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 财经方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>629</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>华泰证券</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>2027届暑期实习+校招提前批-财富管理/机构服务等</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>上海/北京/深圳/南京</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>https://www.htsc.com.cn/</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>630</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>财通资本</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>2027届暑期实习-PE/VC投资</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>https://www.ctcapital.com.cn/</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; PE/VC方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>631</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>洪泰基金</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>2027校园招聘-股权投资管培生</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>战略/战投</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>北京/上海/深圳</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>https://www.hongtai.com/</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>632</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>阿里巴巴</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>2027届实习生-产品/运营/商务拓展</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>策略运营</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>杭州/北京/上海</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>https://talent.alibaba.com/</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>633</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>小红书</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>2027届马当路练习生-产品/运营/市场</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>策略运营</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>北京/上海/深圳/杭州/武汉</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>https://campus.xiaohongshu.com/</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>634</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>快手</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>快Star-2027届校园招聘</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>北京/上海/杭州/深圳</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>https://campus.kuaishou.cn/</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>635</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>金佰利</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>快消</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>2026年暑期实习-管培生</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>管培/人力</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>https://www.kimberly-clark.com.cn/</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 面向2026.9-2027.8毕业</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>636</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>欧莱雅</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>快消</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>2026暑期实习生-可直通2027管培生</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>管培/人力</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>https://www.loreal.com/zh/cn/careers/</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 即将截止</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>637</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>贝泰妮</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>快消</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>2027届管培生</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>管培/人力</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>https://www.betaine.com.cn/</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>638</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>JD RUN-2027届校园招聘</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>北京/上海/深圳/杭州/成都</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>https://campus.jd.com/</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>639</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>安踏集团</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>快消</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>2027届零售管培生</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>管培/人力</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>https://www.anta.com/</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>640</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>中兴通讯</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>2027届秋招提前批-营销类/供应链类</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>深圳/南京/西安/上海/北京</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>https://www.zte.com.cn/</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>641</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>拼多多集团</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>2027届校招-产品&amp;市场类/运营类/综合类</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>策略运营</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>https://careers.pddglobalhr.com/</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17694,7 +21082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17845,6 +21233,35 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>44</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>264</v>
+      </c>
+      <c r="E6" t="n">
+        <v>251</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>飞书秋招合集(24), 网络搜索(20)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>自动更新</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/秋招投递追踪表.xlsx
+++ b/秋招投递追踪表.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q265"/>
+  <dimension ref="A1:Q292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -17727,7 +17727,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -17748,7 +17747,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -17804,7 +17802,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -17825,7 +17822,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -17881,7 +17877,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -17902,7 +17897,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -17958,7 +17952,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -17979,7 +17972,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18035,7 +18027,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18056,7 +18047,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18112,7 +18102,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18133,7 +18122,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18189,7 +18177,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18210,7 +18197,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18266,7 +18252,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18287,7 +18272,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18343,7 +18327,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18364,7 +18347,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18420,7 +18402,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18441,7 +18422,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18497,7 +18477,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18518,7 +18497,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18574,7 +18552,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18595,7 +18572,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18651,7 +18627,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18672,7 +18647,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18728,7 +18702,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18749,7 +18722,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18805,7 +18777,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18826,7 +18797,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18882,7 +18852,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18903,7 +18872,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -18959,7 +18927,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -18980,7 +18947,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19036,7 +19002,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -19057,7 +19022,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19113,7 +19077,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -19134,7 +19097,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19190,7 +19152,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -19211,7 +19172,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19267,7 +19227,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -19288,7 +19247,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19344,7 +19302,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -19365,7 +19322,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19421,7 +19377,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -19442,7 +19397,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19498,7 +19452,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -19519,7 +19472,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19575,7 +19527,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -19596,7 +19547,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19652,7 +19602,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -19673,7 +19622,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19729,7 +19677,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -19750,7 +19697,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19806,7 +19752,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -19827,7 +19772,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19883,7 +19827,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -19904,7 +19847,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -19960,7 +19902,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -19981,7 +19922,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20037,7 +19977,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20058,7 +19997,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20114,7 +20052,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20135,7 +20072,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20191,7 +20127,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20212,7 +20147,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20268,7 +20202,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20289,7 +20222,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20345,7 +20277,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20366,7 +20297,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20422,7 +20352,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20443,7 +20372,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20499,7 +20427,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20520,7 +20447,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20576,7 +20502,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20597,7 +20522,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20653,7 +20577,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
           <t>2026-07-27</t>
@@ -20674,7 +20597,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20730,7 +20652,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20751,7 +20672,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20807,7 +20727,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20828,7 +20747,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20884,7 +20802,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20905,7 +20822,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -20961,7 +20877,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
           <t>招满为止</t>
@@ -20982,7 +20897,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -21038,7 +20952,6 @@
           <t>2027届</t>
         </is>
       </c>
-      <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -21059,7 +20972,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
           <t>待投递</t>
@@ -21068,6 +20980,2166 @@
       <c r="Q265" t="inlineStr">
         <is>
           <t>类型:秋招提前批; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>642</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>雅培</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>生物制药/生命科学</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>运营管理培训生</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>策略运营</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>上海杭州 嘉兴</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>https://www.moseeker.com/position/index/pid/3431275?recom=Olfzxxxxxe&amp;amp</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:未明确，不清楚是否有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>643</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>联合飞机集团</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>无人机总体, 飞控, 发动机, 人工智能, 总体工程师, 强度工程师, 结构工程师, 飞控总体工程师, 前端工程师, 伺服工程师, 后端工程师, 航电系统工程师, 液压系统工程师, 电气工程师, 环控系统工程师, 动力装置防火工程师, 燃油系统工程师, 橡胶工艺工程师, 传动工程师, 地面软件工程师, 软件测试工程师, 起落架工程师, 电机电磁工程师, 适航工程师, 通信测试工程师, 旋翼强度设计, 桨毂结构设计, 试验工程师, 嵌入式系统工程师, 数字硬件工程师, 电机结构工程师, 电控嵌入式工程师, 电控硬件工程师, 硬件工程师, 机载智能功能软件工程师, 安卓开发工程师, C++开发工程师, 动力系统工程师, 控制律工程师, 电控算法工程师, 通信算法工程师, 飞控算法工程师, 规划控制算法工程师, 董事长秘书, 法务专员, 项目经理, 人力专员, 供应链专员, 财务实习生, 融资专员, 产品经理, 飞手, 销售助理, 海外销售, 质量工程师, 六性工程师, 售后技术, 生产工艺工程师, 工业设计工程师, 无人机总体设计, 飞控系统设计, 发动机研制</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>北京, 哈尔滨, 东台, 芜湖, 武汉, 长沙, 深圳, 成都, 什邡, 西安</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>https://www.uatair.com/about/school.html</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:未明确，不清楚是否有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>644</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>麦米电气</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>其他,科技</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>新型电力电子拓扑与控制, 储能变流器并网技术, 电力电子数字化仿真, AIDC数据中心供电技术, 电力电子磁件设计, 激光与电弧物理研究, 涡旋压缩机, 流体仿真, 热设计</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>投资/行研</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>南京, 杭州, 武汉, 长沙, 深圳, 西安</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>https://wecruit.hotjob.cn/SU6282075e0dcad413c09efe26/pb/school.html?projectCode=201301&amp;showProjectBanner=true</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:部分岗位有笔试部分没有</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>645</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>卓驭</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>端到端领航算法工程师, 端到端模型算法工程师, 大模型训练优化算法工程师, 大模型推理优化算法工程师, 多模态大模型预训练算法工程师, 多模态大模型后训练算法工程师, 大模型算法工程师（端到端方向）, 多模态大模型数据与评测算法工程师, 计算机视觉算法工程师(定位建图方向), 计算机视觉算法工程师（传感器标定方向）, 大模型算法工程师（几何重建与动态估计）, 大模型应用工程师（决策规划&amp;机器人方向）, 大模型算法工程师（机器人移动后训练&amp;应用）, 控制算法工程师, 感知算法工程师, 重建仿真算法工程师, 数据闭环算法工程师, 世界模型算法工程师, 强化学习算法工程师, 模型量化算法工程师, 后端开发工程师, 高性能计算工程师, AI应用开发工程师, AI软件开发工程师, 仿真软件开发工程师, 后端开发工程师（AI）, 机器学习平台工程师（数据引擎）, C++软件开发工程师（智驾功能方向）, 后端开发工程师（智能辅助驾驶静态数据）, 具身智能Agent研发工程师（通用移动物理AI）, 前端开发工程师（渲染方向）, Android工程师（HMI方向）, AI应用开发工程师（研效方向）, Android工程师（车载无人机）, 软件开发工程师（决策规划方向）, 后端开发工程师（数据闭环方向）, 硬件工程师, 光学开发工程师, 机械结构工程师, 嵌入式软件工程师, 嵌入式软件开发工程师, 嵌入式驱动开发工程师, 嵌入式软件工程师（车载无人机）, 嵌入式软件开发工程师（中间件）, 嵌入式软件工程师(系统集成方向), 嵌入式驱动开发工程师(传感器方向), 产品测试工程师, AI测试开发工程师（车载无人机）, 网络安全工程师, 功能安全工程师, 功能安全工程师 (L3/L4方向), 系统工程师（基础功能方向）, 系统工程师（智驾功能方向）, 数字化产品经理, 体验设计师（UX）, 辅助驾驶产品经理, 产品工程师-控制器方向, 辅助驾驶产品经理（泊车）</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>投资/行研</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>北京, 上海, 深圳, 香港</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>https://we.zyt.com/campus/jobs</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:卓驭科技校园招聘有测评环节，未明确提及笔试，结论为未明确是否有笔试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>646</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>鹰角网络</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>游戏引擎开发游戏客户端角色模型场景模型</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>https://app.mokahr.com/campus-recruitment/hypergryph/26326#/jobs?page=1&amp;amp</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>647</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>腾讯音乐娱乐集团</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>技术研究:音乐大模型方向 大模型加速方向 歌词大模型方向</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>投资/行研</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>https://join.tencentmusic.com/campus/post/?type=40</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:部分岗位有笔试部分没有</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>648</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>语核科技</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>产品类研发类营销类市场类职能支持类</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/2BCTyDPwgtJCH1UaBRZV1Q</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:未明确，不清楚是否有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>649</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>微源半导体</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>助理模拟设计工程师, 助理芯片验证工程师, 芯片测试工程师, 助理FAE, 销售工程师, 职能管培生</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>上海, 深圳, 成都</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>https://app.mokahr.com/campus-recruitment/lowpowersemi/168412?locale=zh-CN#/</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>650</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>星尘智能</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>技术类产品类市场类职能类</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>https://app.mokahr.com/campus-recruitment/astribot/144862?locale=zh-CN&amp;amp</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:未明确，不清楚是否有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>651</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>芯迈半导体</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>研发类技术类/管理类销售类</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>杭州上海深圳成都</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>https://young.yingjiesheng.com/xyzlogin?ctmid=3e160048-a22b-446f-899d-7bc0a9a6b8db&amp;amp</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:未明确，不清楚是否有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>652</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>柏楚电子</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>软件开发数控系统营销推广传感器设计运动控制研究员感知测试AI算法几何算法 图形学算法前端开发技术支持Java开发产品经理工艺中心助理</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>投资/行研</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>https://fscut.zhiye.com/campus/jobs</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 笔试:部分岗位有笔试部分没有</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>653</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>瑞发科半导体</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>模拟电路设计工程师 数字电路设计工程师IC验证工程师 模拟版图设计工程师数字中端及DFT工程师 信号完整性工程师 硬件工程师硬件测试工程师Linux运维工程师研发采购专员</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/UgfrTEnSN2ViV4yZFAyK5A</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:未明确，不清楚是否有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>654</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>玫瑰岛集团</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>电器/家电</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>管培生岗位:品牌推广市场营销 研发技术 智能制造供应链管理信息技术职能管理 语言类</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>广东中山</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/PeOyOy7EiK6Sv6hxyx_-Cw</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:未明确，不清楚是否有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>655</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>惠升基金</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>行业研究岗、渠道销售岗、债券交易岗、产品岗、营销支持岗、合规风控岗（偏绩效分析方向）、人力资源岗</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>风险管理/合规</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>北京, 上海</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/hn2ff__1ovh047thJFu_6w</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:未明确，不清楚是否有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>656</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>禾迈股份</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>校园大使 光能星探·人才发掘官、绿电种草·品牌发声官、储能操盘·活动执行官、光能纽带·校企联络员</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>销售/市场</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>全国高校</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/1UnDlQHsTOFXN3biUiQ1KQ?scene=1</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>飞书秋招合集</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 笔试:未明确，不清楚是否有笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>657</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>百度</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>2027届校园招聘-产品类/商业分析/综合类</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>商业分析</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>北京/上海/深圳/广州/杭州/成都</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>https://talent.baidu.com/jobs</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 74个细分职位; 5大方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>658</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>2027届应届生-财经专员/税务专员/风控合规</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>财务/审计</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>深圳/北京/上海</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>https://career.huawei.com/</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 财经类岗位; 面向2026.1-2027.12毕业生</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>659</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>科大讯飞</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>2027届常规校招-产品类/职能类</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>合肥/北京/上海/广州/深圳</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>https://campus.iflytek.com/</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 技术类60%+产品类+职能类</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>660</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>滴滴</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>2027届秋招储备实习生-商业分析/金融模型/产品/运营</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>商业分析</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>北京/上海/杭州/广州</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>https://campus.didiglobal.com/</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 面向2026.9-2027.8毕业; 实习转正</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>661</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>中信证券</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>校招培训生-宁波</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>金融策略</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>https://careers.citics.com/</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 面向2026下-2027上毕业</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>662</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>中信证券</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>培训生-北京分公司</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>金融策略</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>https://careers.citics.com/</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>663</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>中信证券</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>校招管培生-上海</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>金融策略</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>https://careers.citics.com/</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>664</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>美团</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>2027届秋招提前批-商业分析/产品/运营</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>商业分析</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>北京/上海/深圳/成都</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>https://campus.meituan.com/</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届; 7月9日开启; 新增AI产品经理等岗位</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>665</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>腾讯</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>2027届实习生招聘-商业分析/产品/运营/市场(可转正)</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>商业分析</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>深圳/北京/上海/广州</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>https://join.qq.com/</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 面向2026.9-2027.12毕业; 优秀实习生可留用</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>666</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>快手</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>快Star-2027届校园招聘-产品/运营/商业分析</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>商业分析</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>北京/上海/杭州/深圳</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>https://campus.kuaishou.cn/</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>667</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>米哈游</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>互联网/科技</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>2027届秋招提前批-产品/运营/市场/商务</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>招满为止</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>https://campus.mihoyo.com/</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>类型:秋招提前批; 届别:2027届</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>668</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>高盛</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>2027届暑期分析师-投行/投资/研究/量化</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>投资/行研</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>北京/上海/香港</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>硕士及以上</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>2027届</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>https://www.goldmansachs.com/careers/</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>网络搜索</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>类型:校招; 届别:2027届; 可转正</t>
         </is>
       </c>
     </row>
@@ -21082,7 +23154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21262,6 +23334,35 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>27</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>291</v>
+      </c>
+      <c r="E7" t="n">
+        <v>278</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>飞书秋招合集(15), 网络搜索(12)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>自动更新</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
